--- a/xls/square_16_tri3_8.xlsx
+++ b/xls/square_16_tri3_8.xlsx
@@ -482,13 +482,13 @@
         <v>384</v>
       </c>
       <c r="I8">
-        <v>3.7577097469856406</v>
+        <v>3.757709667106015</v>
       </c>
       <c r="J8">
-        <v>0.6892552834955402</v>
+        <v>0.6892558530781719</v>
       </c>
       <c r="K8">
-        <v>1.1263549184642363</v>
+        <v>1.126354811859496</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -517,13 +517,13 @@
         <v>486</v>
       </c>
       <c r="I9">
-        <v>-1.758202660417547</v>
+        <v>-1.7582028505385634</v>
       </c>
       <c r="J9">
-        <v>-1.6535944198452588</v>
+        <v>-1.6535944135648664</v>
       </c>
       <c r="K9">
-        <v>-1.053939489900617</v>
+        <v>-1.0539395297836478</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -552,13 +552,13 @@
         <v>600</v>
       </c>
       <c r="I10">
-        <v>-1.7551517667194991</v>
+        <v>-1.7551518381383509</v>
       </c>
       <c r="J10">
-        <v>-1.7991025495904707</v>
+        <v>-1.7991027314073744</v>
       </c>
       <c r="K10">
-        <v>-1.099154027580779</v>
+        <v>-1.0991540717848762</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -587,13 +587,13 @@
         <v>726</v>
       </c>
       <c r="I11">
-        <v>-1.7470216841017379</v>
+        <v>-1.7470215911121167</v>
       </c>
       <c r="J11">
-        <v>-1.7804503188634107</v>
+        <v>-1.7804502784098264</v>
       </c>
       <c r="K11">
-        <v>-0.9704762747437624</v>
+        <v>-0.9704769627030896</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -622,13 +622,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>-1.5073169082204512</v>
+        <v>-1.507317268248869</v>
       </c>
       <c r="J12">
-        <v>-1.1789026639197275</v>
+        <v>-1.1789027666110223</v>
       </c>
       <c r="K12">
-        <v>-0.24946666311150234</v>
+        <v>-0.24946667954972063</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>-1.03109034271349</v>
+        <v>-1.0310903671824363</v>
       </c>
       <c r="J13">
-        <v>-0.785716000601837</v>
+        <v>-0.7857159522668766</v>
       </c>
       <c r="K13">
-        <v>0.13029356526295427</v>
+        <v>0.13029352660091809</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-1.4388568535220188</v>
+        <v>-1.4388571231636096</v>
       </c>
       <c r="J14">
-        <v>-1.1880618089054809</v>
+        <v>-1.18806175709697</v>
       </c>
       <c r="K14">
-        <v>-0.21589568288337568</v>
+        <v>-0.21589568474340218</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -727,13 +727,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-0.42992328490613557</v>
+        <v>-0.4299233370188857</v>
       </c>
       <c r="J15">
-        <v>-0.4123090109236368</v>
+        <v>-0.41230905548920715</v>
       </c>
       <c r="K15">
-        <v>0.5132838413402043</v>
+        <v>0.513283851737999</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -762,13 +762,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-0.972721767216025</v>
+        <v>-0.9727218033436856</v>
       </c>
       <c r="J16">
-        <v>-0.9065726163077013</v>
+        <v>-0.9065726302764533</v>
       </c>
       <c r="K16">
-        <v>0.15410112777566984</v>
+        <v>0.15410112937519407</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -797,13 +797,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>0.008811203892575843</v>
+        <v>0.008811204903486749</v>
       </c>
       <c r="J17">
-        <v>0.00024936137621787074</v>
+        <v>0.000249361592954533</v>
       </c>
       <c r="K17">
-        <v>2.7458866008428817</v>
+        <v>2.7458866259027843</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -832,13 +832,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-0.0004727780937929558</v>
+        <v>-0.0004727780929880721</v>
       </c>
       <c r="J18">
-        <v>-0.0005244196353945213</v>
+        <v>-0.0005244196348210187</v>
       </c>
       <c r="K18">
-        <v>2.8402483482707743</v>
+        <v>2.840248348116681</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -867,13 +867,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-0.0002051174155987887</v>
+        <v>-0.00020511741556251286</v>
       </c>
       <c r="J19">
-        <v>-0.0001605849411183805</v>
+        <v>-0.0001605849410912729</v>
       </c>
       <c r="K19">
-        <v>2.471132763517674</v>
+        <v>2.471132763278267</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -902,13 +902,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.00010337714224638824</v>
+        <v>-0.00010337714223293268</v>
       </c>
       <c r="J20">
-        <v>-9.054437095927414e-5</v>
+        <v>-9.05443709584543e-5</v>
       </c>
       <c r="K20">
-        <v>2.3766957831035858</v>
+        <v>2.3766957831580777</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -937,13 +937,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>8.908505982267022e-7</v>
+        <v>8.908505987088649e-7</v>
       </c>
       <c r="J21">
-        <v>-9.699816142728952e-6</v>
+        <v>-9.699816142294995e-6</v>
       </c>
       <c r="K21">
-        <v>2.0949522239993157</v>
+        <v>2.094952224046337</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -972,13 +972,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>1.0180187318387119e-5</v>
+        <v>1.018018731857998e-5</v>
       </c>
       <c r="J22">
-        <v>1.577776155599924e-7</v>
+        <v>1.577776154635597e-7</v>
       </c>
       <c r="K22">
-        <v>1.958836784798061</v>
+        <v>1.958836785043965</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>2.676239923457701e-6</v>
+        <v>2.676239923361269e-6</v>
       </c>
       <c r="J23">
-        <v>-5.402758557411159e-7</v>
+        <v>-5.402758558857652e-7</v>
       </c>
       <c r="K23">
-        <v>1.7671933013564165</v>
+        <v>1.7671933015922439</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1045,10 +1045,10 @@
         <v>4.120157689895844e-7</v>
       </c>
       <c r="J24">
-        <v>-2.262782545586459e-7</v>
+        <v>-2.262782547032951e-7</v>
       </c>
       <c r="K24">
-        <v>1.4831918694366462</v>
+        <v>1.4831918692342936</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1080,10 +1080,10 @@
         <v>-7.933354285354116e-8</v>
       </c>
       <c r="J25">
-        <v>-8.700281993067924e-8</v>
+        <v>-8.70028197860301e-8</v>
       </c>
       <c r="K25">
-        <v>0.9516663252901006</v>
+        <v>0.9516663251674163</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-1.0071407893634434e-7</v>
+        <v>-1.0071407859882965e-7</v>
       </c>
       <c r="J26">
-        <v>-9.689599149794614e-8</v>
+        <v>-9.68959915943789e-8</v>
       </c>
       <c r="K26">
-        <v>0.9389529549308351</v>
+        <v>0.9389529549516125</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1147,13 +1147,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-9.623758520182852e-8</v>
+        <v>-9.623758515361213e-8</v>
       </c>
       <c r="J27">
-        <v>-9.001939799996929e-8</v>
+        <v>-9.001939804818567e-8</v>
       </c>
       <c r="K27">
-        <v>0.9156780101516298</v>
+        <v>0.915678010356954</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1182,13 +1182,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-9.518432760992102e-8</v>
+        <v>-9.518432765813741e-8</v>
       </c>
       <c r="J28">
-        <v>-8.909639625914405e-8</v>
+        <v>-8.90963961144949e-8</v>
       </c>
       <c r="K28">
-        <v>0.9125501712918631</v>
+        <v>0.9125501713337696</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1217,13 +1217,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-9.37240733555486e-8</v>
+        <v>-9.372407340376499e-8</v>
       </c>
       <c r="J29">
         <v>-8.739818337444939e-8</v>
       </c>
       <c r="K29">
-        <v>0.90864062551913</v>
+        <v>0.9086406255466156</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1255,10 +1255,10 @@
         <v>-9.465614137751086e-8</v>
       </c>
       <c r="J30">
-        <v>-8.878981870289821e-8</v>
+        <v>-8.878981855824906e-8</v>
       </c>
       <c r="K30">
-        <v>0.9134720336244112</v>
+        <v>0.9134720336983698</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1287,13 +1287,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-8.808191579455604e-8</v>
+        <v>-8.808191574633967e-8</v>
       </c>
       <c r="J31">
-        <v>-8.381198141447746e-8</v>
+        <v>-8.381198175199214e-8</v>
       </c>
       <c r="K31">
-        <v>0.9059515731471738</v>
+        <v>0.9059515733001767</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1322,13 +1322,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-9.395412645152559e-8</v>
+        <v>-9.395412625866006e-8</v>
       </c>
       <c r="J32">
-        <v>-8.816784018581095e-8</v>
+        <v>-8.816784023402733e-8</v>
       </c>
       <c r="K32">
-        <v>0.9123360875982971</v>
+        <v>0.9123360873797747</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_8.xlsx
+++ b/xls/square_16_tri3_8.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>289</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>49</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>216</v>
+      </c>
+      <c r="I6">
+        <v>31.884508884892533</v>
+      </c>
+      <c r="J6">
+        <v>32.6413873376467</v>
+      </c>
+      <c r="K6">
+        <v>15.104991268277685</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>81</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>289</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>64</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>294</v>
+      </c>
+      <c r="I7">
+        <v>5.5976861884842615</v>
+      </c>
+      <c r="J7">
+        <v>1.9684557792959088</v>
+      </c>
+      <c r="K7">
+        <v>1.9175763893613595</v>
+      </c>
+    </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>11</v>
